--- a/xlsx/tests/templates/yearly_calendar.xlsx
+++ b/xlsx/tests/templates/yearly_calendar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/v0.8.02/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/v0.9/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88D010F-C510-4B4C-B6B5-F84C4CC698E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2531C4B-58CA-3E4B-B4D2-C24387561A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="-19400" windowWidth="33960" windowHeight="17260" xr2:uid="{6F0581DF-A6A1-8847-8CD1-D7A1DAEC65B8}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{6F0581DF-A6A1-8847-8CD1-D7A1DAEC65B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Yearly calendar" sheetId="1" r:id="rId1"/>
@@ -2411,6 +2411,7 @@
       <c r="AG19" s="9"/>
     </row>
     <row r="20" spans="1:33" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
       <c r="B20" s="5" t="str">
         <f ca="1"/>
         <v/>
@@ -3533,7 +3534,7 @@
       </c>
       <c r="B2" s="13">
         <f ca="1">NOW()</f>
-        <v>46233.603531944442</v>
+        <v>46309.700157407409</v>
       </c>
     </row>
   </sheetData>
